--- a/area form produksi.xlsx
+++ b/area form produksi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="187">
   <si>
     <t>bulanan</t>
   </si>
@@ -574,6 +574,12 @@
   </si>
   <si>
     <t>cek list</t>
+  </si>
+  <si>
+    <t>cek</t>
+  </si>
+  <si>
+    <t>kapan di input? Jika tidak di input tidak bisa melakukan pergantian batch di mesin tersebut?</t>
   </si>
 </sst>
 </file>
@@ -659,14 +665,8 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -674,11 +674,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -990,466 +996,466 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="8" t="s">
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="2" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="10" t="s">
+      <c r="J7" s="2"/>
+      <c r="K7" s="11" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="10"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="11"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="10"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="11"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="10"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="11" t="s">
+      <c r="J11" s="2"/>
+      <c r="K11" s="8" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1492,18 +1498,18 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
@@ -1550,104 +1556,104 @@
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="6" t="s">
         <v>173</v>
       </c>
     </row>
@@ -1691,20 +1697,20 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
@@ -1871,10 +1877,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -1884,445 +1890,454 @@
     <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="83.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:17">
+      <c r="A1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="3" t="s">
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="3" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="3" t="s">
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="3" t="s">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="12" t="s">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="3" t="s">
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" t="s">
+        <v>185</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2362,22 +2377,22 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="2" t="s">
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
@@ -2415,7 +2430,7 @@
       <c r="B3" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>87</v>
       </c>
       <c r="D3" t="s">
@@ -2424,23 +2439,23 @@
       <c r="E3" t="s">
         <v>88</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>90</v>
       </c>
       <c r="H3" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1">
       <c r="A4" t="s">
@@ -2470,11 +2485,11 @@
       <c r="I4" t="s">
         <v>99</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2498,353 +2513,353 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="9" t="s">
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="3"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/area form produksi.xlsx
+++ b/area form produksi.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="75" windowWidth="20055" windowHeight="7935" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="75" windowWidth="20055" windowHeight="7935" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="SANITASI" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="189">
   <si>
     <t>bulanan</t>
   </si>
@@ -580,6 +580,12 @@
   </si>
   <si>
     <t>kapan di input? Jika tidak di input tidak bisa melakukan pergantian batch di mesin tersebut?</t>
+  </si>
+  <si>
+    <t>pemusnahan bad produk dari reject</t>
+  </si>
+  <si>
+    <t>kupas rework dari rework</t>
   </si>
 </sst>
 </file>
@@ -1667,7 +1673,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
@@ -1865,6 +1871,16 @@
       </c>
       <c r="M5" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/area form produksi.xlsx
+++ b/area form produksi.xlsx
@@ -4,22 +4,23 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="75" windowWidth="20055" windowHeight="7935" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="75" windowWidth="20055" windowHeight="7935" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="SANITASI" sheetId="1" r:id="rId1"/>
     <sheet name="MP" sheetId="2" r:id="rId2"/>
-    <sheet name="PACKING" sheetId="3" r:id="rId3"/>
-    <sheet name="FILLER" sheetId="4" r:id="rId4"/>
+    <sheet name="FILLER" sheetId="4" r:id="rId3"/>
+    <sheet name="SUSUN" sheetId="7" r:id="rId4"/>
     <sheet name="RETORT" sheetId="5" r:id="rId5"/>
-    <sheet name="KR MP" sheetId="6" r:id="rId6"/>
+    <sheet name="PACKING" sheetId="3" r:id="rId6"/>
+    <sheet name="KR MP" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="206">
   <si>
     <t>bulanan</t>
   </si>
@@ -513,15 +514,9 @@
     <t>pilih area, langsung muncul item dan sub area tinggal ceklist</t>
   </si>
   <si>
-    <t>form checklist kebersihan sanitasi baru</t>
-  </si>
-  <si>
     <t>idem</t>
   </si>
   <si>
-    <t>area, forman, spv, inspektor sanitasi</t>
-  </si>
-  <si>
     <t>pengecekan mesin</t>
   </si>
   <si>
@@ -586,6 +581,63 @@
   </si>
   <si>
     <t>kupas rework dari rework</t>
+  </si>
+  <si>
+    <t>area,tanggal, checker sanitasi, insperktor sanitasi, spv produksi</t>
+  </si>
+  <si>
+    <t>form checklist kebersihan sanitasi ALL AREA baru</t>
+  </si>
+  <si>
+    <t>planning</t>
+  </si>
+  <si>
+    <t>area, tanggal, ch, fm, spv</t>
+  </si>
+  <si>
+    <t>per sub area / jenis</t>
+  </si>
+  <si>
+    <t>pilih sub area</t>
+  </si>
+  <si>
+    <t>cek list item</t>
+  </si>
+  <si>
+    <t>paraf prod = user input</t>
+  </si>
+  <si>
+    <t>penggunaan rework</t>
+  </si>
+  <si>
+    <t>tanggal, opr, kr, spv</t>
+  </si>
+  <si>
+    <t>tiap batch kupas</t>
+  </si>
+  <si>
+    <t>tanggal masuk CS &amp; kupas</t>
+  </si>
+  <si>
+    <t>qty masuk CS</t>
+  </si>
+  <si>
+    <t>qty pemakaian</t>
+  </si>
+  <si>
+    <t>kode batch saat penggunaan</t>
+  </si>
+  <si>
+    <t>sisa rework</t>
+  </si>
+  <si>
+    <t>temua plastik dan metal</t>
+  </si>
+  <si>
+    <t>acc qc</t>
+  </si>
+  <si>
+    <t>acc opr = user input</t>
   </si>
 </sst>
 </file>
@@ -990,7 +1042,7 @@
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40.140625" bestFit="1" customWidth="1"/>
@@ -1300,13 +1352,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>140</v>
@@ -1328,7 +1380,7 @@
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1478,10 +1530,11 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="40.42578125" bestFit="1" customWidth="1"/>
@@ -1636,31 +1689,31 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>127</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>35</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -1672,226 +1725,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2" t="s">
-        <v>45</v>
-      </c>
-      <c r="M2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N2" t="s">
-        <v>47</v>
-      </c>
-      <c r="O2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" t="s">
-        <v>106</v>
-      </c>
-      <c r="H4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I4" t="s">
-        <v>108</v>
-      </c>
-      <c r="J4" t="s">
-        <v>109</v>
-      </c>
-      <c r="K4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F5" t="s">
-        <v>104</v>
-      </c>
-      <c r="G5" t="s">
-        <v>114</v>
-      </c>
-      <c r="H5" t="s">
-        <v>105</v>
-      </c>
-      <c r="I5" t="s">
-        <v>106</v>
-      </c>
-      <c r="J5" t="s">
-        <v>115</v>
-      </c>
-      <c r="K5" t="s">
-        <v>116</v>
-      </c>
-      <c r="L5" t="s">
-        <v>117</v>
-      </c>
-      <c r="M5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" t="s">
-        <v>188</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="E1:P1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2075,37 +1908,37 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>127</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -2115,31 +1948,31 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>35</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -2149,7 +1982,7 @@
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -2352,7 +2185,91 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>185</v>
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E1:P1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
+        <v>194</v>
+      </c>
+      <c r="J2" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2365,7 +2282,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
@@ -2507,6 +2424,38 @@
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
     </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G5" t="s">
+        <v>193</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>194</v>
+      </c>
+      <c r="J5" t="s">
+        <v>179</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="E1:J1"/>
@@ -2516,6 +2465,303 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" t="s">
+        <v>108</v>
+      </c>
+      <c r="J4" t="s">
+        <v>109</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" t="s">
+        <v>106</v>
+      </c>
+      <c r="J5" t="s">
+        <v>115</v>
+      </c>
+      <c r="K5" t="s">
+        <v>116</v>
+      </c>
+      <c r="L5" t="s">
+        <v>117</v>
+      </c>
+      <c r="M5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F6" t="s">
+        <v>192</v>
+      </c>
+      <c r="G6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" t="s">
+        <v>194</v>
+      </c>
+      <c r="J6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" t="s">
+        <v>198</v>
+      </c>
+      <c r="H7" t="s">
+        <v>199</v>
+      </c>
+      <c r="I7" t="s">
+        <v>200</v>
+      </c>
+      <c r="J7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K7" t="s">
+        <v>202</v>
+      </c>
+      <c r="L7" t="s">
+        <v>203</v>
+      </c>
+      <c r="M7" t="s">
+        <v>204</v>
+      </c>
+      <c r="N7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E1:P1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15"/>
